--- a/data/Alino_Property_Accounts.xlsx
+++ b/data/Alino_Property_Accounts.xlsx
@@ -123,7 +123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="354">
   <si>
     <t xml:space="preserve">Alino Property Ltd</t>
   </si>
@@ -152,9 +152,6 @@
     <t xml:space="preserve">Cost of sales</t>
   </si>
   <si>
-    <t xml:space="preserve">Building materials</t>
-  </si>
-  <si>
     <t xml:space="preserve">Subcontractor / building costs</t>
   </si>
   <si>
@@ -170,6 +167,9 @@
     <t xml:space="preserve">Administrative expenses</t>
   </si>
   <si>
+    <t xml:space="preserve">Repairs &amp; maintenance (Seyat Can materials)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tenancy set-up costs (Goodlord)</t>
   </si>
   <si>
@@ -215,6 +215,9 @@
     <t xml:space="preserve">Investment property – 36 Cairnsford Road (cost)</t>
   </si>
   <si>
+    <t xml:space="preserve">Improvements – 36 Cairnsford Road (Seyat Can materials)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Investment property – 30 Strensall Road (cost – see Notes)</t>
   </si>
   <si>
@@ -323,6 +326,15 @@
     <t xml:space="preserve">Not provided – company appears to own it (MR01 charge registered); enter original cost</t>
   </si>
   <si>
+    <t xml:space="preserve">Seyat Can materials £4,500 – treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asset = improvement to 36 Cairnsford Rd (balance sheet). Repairs = repairs &amp; maintenance expense (P&amp;L). Choose from the list.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Records used</t>
   </si>
   <si>
@@ -371,7 +383,7 @@
     <t xml:space="preserve">10. 'Other income received' (£7,132 – Njiaga, Siewe, Deufi, Kouchoufondjo) is treated as income because no purpose is stated. If any of it is a loan or capital, reclassify it.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Seyat Can 'Material' (£4,500) and payments to Ahmed Sayyed/Alino Ltd (£2,200) are cost of sales. If they were improvements to a property, capitalise them instead.</t>
+    <t xml:space="preserve">11. Seyat Can 'Material' (£4,500, Sep/Oct-25) is controlled by the switch above. Default 'Asset': it is capitalised as an improvement to 36 Cairnsford Road (bought 17/07/2025) because it was paid 2–3 months after purchase. Use 'Repairs' if it only restored existing items like-for-like. Payments to Ahmed Sayyed/Alino Ltd (£2,200) are cost of sales.</t>
   </si>
   <si>
     <t xml:space="preserve">12. No depreciation is charged on investment property, which is held at cost (FRS 102 s16 fair value not assessed). No corporation tax is due, because there is a loss.</t>
@@ -398,12 +410,12 @@
     <t xml:space="preserve">Investment property – 36 Cairnsford Rd</t>
   </si>
   <si>
-    <t xml:space="preserve">Asset</t>
-  </si>
-  <si>
     <t xml:space="preserve">Investment property – 30 Strensall Rd</t>
   </si>
   <si>
+    <t xml:space="preserve">Property improvements – 36 Cairnsford Rd</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cash at bank – share capital not traced</t>
   </si>
   <si>
@@ -431,6 +443,9 @@
     <t xml:space="preserve">Other income (to confirm)</t>
   </si>
   <si>
+    <t xml:space="preserve">Repairs &amp; maintenance</t>
+  </si>
+  <si>
     <t xml:space="preserve">Expense</t>
   </si>
   <si>
@@ -530,7 +545,13 @@
     <t xml:space="preserve">Sep-25–Oct-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Building materials – Seyat Can</t>
+    <t xml:space="preserve">Seyat Can materials – capitalised (if switch = Asset)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seyat Can materials – repairs (if switch = Repairs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seyat Can materials paid</t>
   </si>
   <si>
     <t xml:space="preserve">Oct-25 &amp; Dec-25</t>
@@ -1170,13 +1191,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\£#,##0.00;&quot;(£&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="168" formatCode="0"/>
-    <numFmt numFmtId="169" formatCode="\£#,##0.00;&quot;-£&quot;#,##0.00;\-"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -1344,7 +1364,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1497,39 +1517,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1908,8 +1896,8 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Building materials")</f>
-        <v>4500</v>
+        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Subcontractor / building costs")</f>
+        <v>2200</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1917,40 +1905,40 @@
         <v>10</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Subcontractor / building costs")</f>
+        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Rent payable")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <f aca="false">SUM(B13:B14)</f>
         <v>2200</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Rent payable")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="7" t="n">
-        <f aca="false">SUM(B13:B15)</f>
-        <v>6700</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="C17" s="7" t="n">
+        <f aca="false">C10-C15</f>
+        <v>11132</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="7" t="n">
-        <f aca="false">C10-C16</f>
-        <v>6632</v>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="5" t="s">
         <v>14</v>
+      </c>
+      <c r="B20" s="6" t="n">
+        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Repairs &amp; maintenance")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1976,7 +1964,7 @@
         <v>17</v>
       </c>
       <c r="C23" s="7" t="n">
-        <f aca="false">SUM(B21:B22)</f>
+        <f aca="false">SUM(B20:B22)</f>
         <v>0</v>
       </c>
     </row>
@@ -1985,8 +1973,8 @@
         <v>18</v>
       </c>
       <c r="C25" s="7" t="n">
-        <f aca="false">C18-C23</f>
-        <v>6632</v>
+        <f aca="false">C17-C23</f>
+        <v>11132</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2027,7 +2015,7 @@
       </c>
       <c r="C32" s="7" t="n">
         <f aca="false">C25-C30</f>
-        <v>-12255.05</v>
+        <v>-7755.05</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2045,7 +2033,7 @@
       </c>
       <c r="C35" s="8" t="n">
         <f aca="false">C32-C34</f>
-        <v>-12255.05</v>
+        <v>-7755.05</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2076,273 +2064,273 @@
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="13" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="41" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="42" t="n">
+      <c r="C4" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – purchase price")</f>
         <v>462000</v>
       </c>
-      <c r="C5" s="43"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="41" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="42" t="n">
+      <c r="C5" s="35"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – Stamp Duty (SDLT)")</f>
         <v>36200</v>
       </c>
-      <c r="C6" s="43" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="41" t="s">
-        <v>319</v>
-      </c>
-      <c r="B7" s="42" t="n">
+      <c r="C6" s="35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="B7" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Property cost – legal &amp; acquisition fees")</f>
         <v>1743.94</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="44" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="45" t="n">
+      <c r="C7" s="35" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="24" t="s">
+        <v>328</v>
+      </c>
+      <c r="B8" s="25" t="n">
         <f aca="false">SUM(B5:B7)</f>
         <v>499943.94</v>
       </c>
-      <c r="C8" s="44"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="13" t="s">
+      <c r="C8" s="24"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="B10" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="s">
-        <v>323</v>
-      </c>
-      <c r="B11" s="42" t="n">
+      <c r="C10" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B11" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Finance cost – Cairnsford mortgage")</f>
         <v>715</v>
       </c>
-      <c r="C11" s="43" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="41" t="s">
-        <v>325</v>
-      </c>
-      <c r="B12" s="42" t="n">
+      <c r="C11" s="35" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="B12" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F$2:$F$41,'Completion Lines'!$G$2:$G$41,"Finance cost – Strensall remortgage")</f>
         <v>1670</v>
       </c>
-      <c r="C12" s="43" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="44" t="s">
+      <c r="C12" s="35" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="45" t="n">
+      <c r="B13" s="25" t="n">
         <f aca="false">SUM(B11:B12)</f>
         <v>2385</v>
       </c>
-      <c r="C13" s="44"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="B15" s="13" t="s">
+      <c r="C13" s="24"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B15" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="B16" s="42" t="n">
+      <c r="C15" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Together Commercial mortgage (net)")</f>
         <v>311938.6</v>
       </c>
-      <c r="C16" s="43" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="B17" s="42" t="n">
+      <c r="C16" s="35" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="B17" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Transfer – Strensall proceeds to Cairnsford",'Completion Lines'!$A$2:$A$41,"36 Cairnsford Rd – Purchase (17/07/2025)")</f>
         <v>131958</v>
       </c>
-      <c r="C17" s="43" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
-        <v>332</v>
-      </c>
-      <c r="B18" s="42" t="n">
+      <c r="C17" s="35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B18" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Alvine Tchega")</f>
         <v>18362.34</v>
       </c>
-      <c r="C18" s="43" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="41" t="s">
-        <v>334</v>
-      </c>
-      <c r="B19" s="42" t="n">
+      <c r="C18" s="35" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B19" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – Kakmeni")</f>
         <v>38000</v>
       </c>
-      <c r="C19" s="43" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="41" t="s">
-        <v>336</v>
-      </c>
-      <c r="B20" s="42" t="n">
+      <c r="C19" s="35" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" s="23" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$C$2:$C$41,'Completion Lines'!$G$2:$G$41,"Funding – money on account",'Completion Lines'!$A$2:$A$41,"36 Cairnsford Rd – Purchase (17/07/2025)")</f>
         <v>400</v>
       </c>
-      <c r="C20" s="43"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="44" t="s">
-        <v>337</v>
-      </c>
-      <c r="B21" s="45" t="n">
+      <c r="C20" s="35"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <f aca="false">SUM(B16:B20)</f>
         <v>500658.94</v>
       </c>
-      <c r="C21" s="44"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="B23" s="13" t="s">
+      <c r="C21" s="24"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="B23" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="B24" s="42" t="n">
+      <c r="C23" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="B24" s="23" t="n">
         <f aca="false">B8+B11</f>
         <v>500658.94</v>
       </c>
-      <c r="C24" s="43"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="B25" s="42" t="n">
+      <c r="C24" s="35"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="B25" s="23" t="n">
         <f aca="false">B21</f>
         <v>500658.94</v>
       </c>
-      <c r="C25" s="43"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B26" s="46" t="n">
+      <c r="C25" s="35"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="31" t="n">
         <f aca="false">ROUND(B24-B25,2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="B28" s="13" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B28" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="B29" s="42" t="n">
+      <c r="C28" s="32" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="B29" s="23" t="n">
         <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$E:$E,"10395974-002")</f>
         <v>10699.15</v>
       </c>
-      <c r="C29" s="43" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="B30" s="42" t="n">
+      <c r="C29" s="35" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="B30" s="23" t="n">
         <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$E:$E,"10395973-002")</f>
         <v>5802.9</v>
       </c>
-      <c r="C30" s="43" t="s">
-        <v>346</v>
+      <c r="C30" s="35" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -2361,7 +2349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="62"/>
@@ -2411,29 +2399,29 @@
         <v>30</v>
       </c>
       <c r="B8" s="6" t="n">
+        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Property improvements – 36 Cairnsford Rd")</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Investment property – 30 Strensall Rd")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="C9" s="7" t="n">
-        <f aca="false">SUM(B7:B8)</f>
-        <v>499943.94</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2"/>
+      <c r="C10" s="7" t="n">
+        <f aca="false">SUM(B7:B9)</f>
+        <v>504443.94</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Cash at bank – Monzo")</f>
-        <v>129.950000000001</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2441,29 +2429,29 @@
         <v>33</v>
       </c>
       <c r="B13" s="6" t="n">
+        <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Cash at bank – Monzo")</f>
+        <v>129.950000000001</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="6" t="n">
         <f aca="false">SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Cash at bank – share capital not traced")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="C14" s="7" t="n">
-        <f aca="false">SUM(B12:B13)</f>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2"/>
+      <c r="C15" s="7" t="n">
+        <f aca="false">SUM(B13:B14)</f>
         <v>129.950000000001</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Director's loan – Alvine Tchega")</f>
-        <v>21462.34</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2471,8 +2459,8 @@
         <v>36</v>
       </c>
       <c r="B17" s="6" t="n">
-        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Loan – Kakmeni")</f>
-        <v>39000</v>
+        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Director's loan – Alvine Tchega")</f>
+        <v>21462.34</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2480,8 +2468,8 @@
         <v>37</v>
       </c>
       <c r="B18" s="6" t="n">
-        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Loan – The Kulture Bar")</f>
-        <v>6400</v>
+        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Loan – Kakmeni")</f>
+        <v>39000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2489,47 +2477,47 @@
         <v>38</v>
       </c>
       <c r="B19" s="6" t="n">
+        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Loan – The Kulture Bar")</f>
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="n">
         <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Suspense – other bank account (not provided)")</f>
         <v>-0</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="C20" s="7" t="n">
-        <f aca="false">-SUM(B16:B19)</f>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2"/>
+      <c r="C21" s="7" t="n">
+        <f aca="false">-SUM(B17:B20)</f>
         <v>-66862.34</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <f aca="false">C14+C20</f>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <f aca="false">C15+C21</f>
         <v>-66732.39</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <f aca="false">C9+C22</f>
-        <v>433211.55</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="C25" s="7" t="n">
+        <f aca="false">C10+C23</f>
+        <v>437711.55</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B27" s="6" t="n">
-        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Mortgage – Together Commercial (Cairnsford)")</f>
-        <v>311938.6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2537,38 +2525,38 @@
         <v>43</v>
       </c>
       <c r="B28" s="6" t="n">
+        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Mortgage – Together Commercial (Cairnsford)")</f>
+        <v>311938.6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="6" t="n">
         <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Mortgage – Together Commercial (Strensall)")</f>
         <v>133528</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2"/>
-      <c r="C29" s="7" t="n">
-        <f aca="false">-SUM(B27:B28)</f>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="C30" s="7" t="n">
+        <f aca="false">-SUM(B28:B29)</f>
         <v>-445466.6</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <f aca="false">C24+C29</f>
-        <v>-12255.05</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="C32" s="8" t="n">
+        <f aca="false">C25+C30</f>
+        <v>-7755.04999999999</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B34" s="6" t="n">
-        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Share capital")</f>
-        <v>-0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2576,31 +2564,40 @@
         <v>47</v>
       </c>
       <c r="B35" s="6" t="n">
+        <f aca="false">-SUMIFS('Trial Balance'!$E:$E,'Trial Balance'!$A:$A,"Share capital")</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B36" s="6" t="n">
         <f aca="false">'P&amp;L'!C35</f>
-        <v>-12255.05</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <f aca="false">SUM(B34:B35)</f>
-        <v>-12255.05</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
+        <v>-7755.05</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="9" t="n">
-        <f aca="false">ROUND(C31-C36,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
+      <c r="C37" s="8" t="n">
+        <f aca="false">SUM(B35:B36)</f>
+        <v>-7755.05</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <f aca="false">ROUND(C32-C37,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -2619,7 +2616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -2629,204 +2626,214 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B5" s="11" t="n">
         <v>133385.92</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>7712</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1511.47</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
         <v>66</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>67</v>
+      <c r="A12" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
     </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A21:C21"/>
@@ -2839,10 +2846,15 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B4" type="list">
       <formula1>"Yes,No"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B10" type="list">
+      <formula1>"Asset,Repairs"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2861,7 +2873,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -2871,27 +2883,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C2" s="6" t="n">
         <f aca="false">IF(E2&gt;0,E2,0)</f>
@@ -2908,10 +2920,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C3" s="6" t="n">
         <f aca="false">IF(E3&gt;0,E3,0)</f>
@@ -2928,14 +2940,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C4" s="6" t="n">
         <f aca="false">IF(E4&gt;0,E4,0)</f>
-        <v>129.950000000001</v>
+        <v>4500</v>
       </c>
       <c r="D4" s="6" t="n">
         <f aca="false">IF(E4&lt;0,-E4,0)</f>
@@ -2943,19 +2955,19 @@
       </c>
       <c r="E4" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A4)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A4)</f>
-        <v>129.950000000001</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">IF(E5&gt;0,E5,0)</f>
-        <v>0</v>
+        <v>129.950000000001</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">IF(E5&lt;0,-E5,0)</f>
@@ -2963,15 +2975,15 @@
       </c>
       <c r="E5" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A5)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A5)</f>
-        <v>0</v>
+        <v>129.950000000001</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">IF(E6&gt;0,E6,0)</f>
@@ -2979,19 +2991,19 @@
       </c>
       <c r="D6" s="6" t="n">
         <f aca="false">IF(E6&lt;0,-E6,0)</f>
-        <v>311938.6</v>
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A6)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A6)</f>
-        <v>-311938.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">IF(E7&gt;0,E7,0)</f>
@@ -2999,19 +3011,19 @@
       </c>
       <c r="D7" s="6" t="n">
         <f aca="false">IF(E7&lt;0,-E7,0)</f>
-        <v>133528</v>
+        <v>311938.6</v>
       </c>
       <c r="E7" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A7)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A7)</f>
-        <v>-133528</v>
+        <v>-311938.6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">IF(E8&gt;0,E8,0)</f>
@@ -3019,19 +3031,19 @@
       </c>
       <c r="D8" s="6" t="n">
         <f aca="false">IF(E8&lt;0,-E8,0)</f>
-        <v>21462.34</v>
+        <v>133528</v>
       </c>
       <c r="E8" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A8)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A8)</f>
-        <v>-21462.34</v>
+        <v>-133528</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">IF(E9&gt;0,E9,0)</f>
@@ -3039,11 +3051,11 @@
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">IF(E9&lt;0,-E9,0)</f>
-        <v>39000</v>
+        <v>21462.34</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A9)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A9)</f>
-        <v>-39000</v>
+        <v>-21462.34</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3051,7 +3063,7 @@
         <v>37</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">IF(E10&gt;0,E10,0)</f>
@@ -3059,11 +3071,11 @@
       </c>
       <c r="D10" s="6" t="n">
         <f aca="false">IF(E10&lt;0,-E10,0)</f>
-        <v>6400</v>
+        <v>39000</v>
       </c>
       <c r="E10" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A10)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A10)</f>
-        <v>-6400</v>
+        <v>-39000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3071,7 +3083,7 @@
         <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">IF(E11&gt;0,E11,0)</f>
@@ -3079,16 +3091,16 @@
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">IF(E11&lt;0,-E11,0)</f>
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A11)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A11)</f>
-        <v>0</v>
+        <v>-6400</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>99</v>
@@ -3108,10 +3120,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">IF(E13&gt;0,E13,0)</f>
@@ -3119,19 +3131,19 @@
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">IF(E13&lt;0,-E13,0)</f>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A13)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A13)</f>
-        <v>-2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">IF(E14&gt;0,E14,0)</f>
@@ -3139,19 +3151,19 @@
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">IF(E14&lt;0,-E14,0)</f>
-        <v>7132</v>
+        <v>2200</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A14)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A14)</f>
-        <v>-7132</v>
+        <v>-2200</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C15" s="6" t="n">
         <f aca="false">IF(E15&gt;0,E15,0)</f>
@@ -3159,43 +3171,43 @@
       </c>
       <c r="D15" s="6" t="n">
         <f aca="false">IF(E15&lt;0,-E15,0)</f>
-        <v>4000</v>
+        <v>7132</v>
       </c>
       <c r="E15" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A15)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A15)</f>
-        <v>-4000</v>
+        <v>-7132</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="6" t="n">
         <f aca="false">IF(E16&gt;0,E16,0)</f>
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="D16" s="6" t="n">
         <f aca="false">IF(E16&lt;0,-E16,0)</f>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="E16" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A16)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A16)</f>
-        <v>4500</v>
+        <v>-4000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C17" s="6" t="n">
         <f aca="false">IF(E17&gt;0,E17,0)</f>
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="D17" s="6" t="n">
         <f aca="false">IF(E17&lt;0,-E17,0)</f>
@@ -3203,19 +3215,19 @@
       </c>
       <c r="E17" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A17)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A17)</f>
-        <v>2200</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">IF(E18&gt;0,E18,0)</f>
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">IF(E18&lt;0,-E18,0)</f>
@@ -3223,15 +3235,15 @@
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A18)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A18)</f>
-        <v>0</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C19" s="6" t="n">
         <f aca="false">IF(E19&gt;0,E19,0)</f>
@@ -3248,10 +3260,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C20" s="6" t="n">
         <f aca="false">IF(E20&gt;0,E20,0)</f>
@@ -3268,14 +3280,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C21" s="6" t="n">
         <f aca="false">IF(E21&gt;0,E21,0)</f>
-        <v>16502.05</v>
+        <v>0</v>
       </c>
       <c r="D21" s="6" t="n">
         <f aca="false">IF(E21&lt;0,-E21,0)</f>
@@ -3283,19 +3295,19 @@
       </c>
       <c r="E21" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A21)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A21)</f>
-        <v>16502.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>21</v>
+        <v>109</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C22" s="6" t="n">
         <f aca="false">IF(E22&gt;0,E22,0)</f>
-        <v>2385</v>
+        <v>16502.05</v>
       </c>
       <c r="D22" s="6" t="n">
         <f aca="false">IF(E22&lt;0,-E22,0)</f>
@@ -3303,41 +3315,61 @@
       </c>
       <c r="E22" s="6" t="n">
         <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A22)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A22)</f>
+        <v>16502.05</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <f aca="false">IF(E23&gt;0,E23,0)</f>
         <v>2385</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <f aca="false">SUM(C2:C22)</f>
+      <c r="D23" s="6" t="n">
+        <f aca="false">IF(E23&lt;0,-E23,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <f aca="false">SUMIFS(Journals!$E:$E,Journals!$D:$D,$A23)-SUMIFS(Journals!$F:$F,Journals!$D:$D,$A23)</f>
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <f aca="false">SUM(C2:C23)</f>
         <v>525660.94</v>
       </c>
-      <c r="D23" s="14" t="n">
-        <f aca="false">SUM(D2:D22)</f>
+      <c r="D24" s="14" t="n">
+        <f aca="false">SUM(D2:D23)</f>
         <v>525660.94</v>
       </c>
-      <c r="E23" s="14" t="n">
-        <f aca="false">SUM(E2:E22)</f>
+      <c r="E24" s="14" t="n">
+        <f aca="false">SUM(E2:E23)</f>
         <v>2.5465851649642E-011</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <f aca="false">ROUND(SUM(Journals!E2:E34)-SUM(Journals!F2:F34)-E23,2)</f>
-        <v>-0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E25" s="15" t="n">
-        <f aca="false">ROUND(E4-'Monzo Reconciliation'!F10,2)</f>
+        <f aca="false">ROUND(SUM(Journals!E2:E35)-SUM(Journals!F2:F35)-E24,2)</f>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <f aca="false">ROUND(E5-'Monzo Reconciliation'!F10,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -3357,7 +3389,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3370,25 +3402,25 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3396,13 +3428,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E2" s="16" t="n">
         <f aca="false">SUMIFS('Completion Lines'!$F:$F,'Completion Lines'!$G:$G,"Property cost – purchase price")+SUMIFS('Completion Lines'!$F:$F,'Completion Lines'!$G:$G,"Property cost – Stamp Duty (SDLT)")+SUMIFS('Completion Lines'!$F:$F,'Completion Lines'!$G:$G,"Property cost – legal &amp; acquisition fees")</f>
@@ -3412,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3420,10 +3452,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>21</v>
@@ -3436,7 +3468,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,10 +3476,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>21</v>
@@ -3460,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3468,13 +3500,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>0</v>
@@ -3484,7 +3516,7 @@
         <v>311938.6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3492,13 +3524,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -3508,7 +3540,7 @@
         <v>133528</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3516,13 +3548,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>0</v>
@@ -3532,7 +3564,7 @@
         <v>18862.34</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3540,13 +3572,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>0</v>
@@ -3556,7 +3588,7 @@
         <v>38000</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3564,13 +3596,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Rent received – Kakmeni")</f>
@@ -3580,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3588,10 +3620,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>4</v>
@@ -3604,7 +3636,7 @@
         <v>2200</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3612,13 +3644,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Other income received")</f>
@@ -3628,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3636,13 +3668,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>0</v>
@@ -3652,7 +3684,7 @@
         <v>7132</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3660,13 +3692,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building work income (Alino Ltd)")</f>
@@ -3676,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3684,10 +3716,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>5</v>
@@ -3700,7 +3732,7 @@
         <v>4000</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3708,13 +3740,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Loans received",'Monzo Transactions'!$D:$D,"THE KULTURE BAR AN")</f>
@@ -3724,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3732,13 +3764,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>0</v>
@@ -3748,7 +3780,7 @@
         <v>6400</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3756,13 +3788,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Loans received",'Monzo Transactions'!$D:$D,"KAKMENI J")</f>
@@ -3772,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3780,13 +3812,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="6" t="n">
         <v>0</v>
@@ -3796,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3804,13 +3836,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="16" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Director transfers (Alvine Tchega)")</f>
@@ -3820,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3828,13 +3860,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -3844,7 +3876,7 @@
         <v>2600</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,23 +3884,23 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="E21" s="16" t="n">
-        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building materials (Seyat Can)")</f>
+        <f aca="false">IF(Notes!$B$10="Asset",-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building materials (Seyat Can)"),0)</f>
         <v>4500</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3876,23 +3908,23 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building materials (Seyat Can)")</f>
-        <v>4500</v>
+        <v>106</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <f aca="false">IF(Notes!$B$10="Repairs",-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building materials (Seyat Can)"),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3900,23 +3932,23 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Payments to Alino / Ahmed Sayyed")</f>
-        <v>2200</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Building materials (Seyat Can)")</f>
+        <v>4500</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3924,23 +3956,23 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E24" s="16" t="n">
         <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Payments to Alino / Ahmed Sayyed")</f>
         <v>2200</v>
       </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3948,23 +3980,23 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Mortgage*")</f>
-        <v>16502.05</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="16" t="n">
+        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Payments to Alino / Ahmed Sayyed")</f>
+        <v>2200</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3972,23 +4004,23 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="16" t="n">
+        <v>109</v>
+      </c>
+      <c r="E26" s="16" t="n">
         <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Mortgage*")</f>
         <v>16502.05</v>
       </c>
+      <c r="F26" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G26" s="5" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3996,23 +4028,23 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>0</v>
+        <v>33</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <f aca="false">-SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,"Mortgage*")</f>
+        <v>16502.05</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4020,23 +4052,23 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="E28" s="16" t="n">
-        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$6,0)</f>
+        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$5,0)</f>
         <v>0</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4044,23 +4076,23 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" s="16" t="n">
-        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$7,0)</f>
+        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$6,0)</f>
         <v>0</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,23 +4100,23 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$5+Notes!$B$6+Notes!$B$7,0)</f>
+        <v>16</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4092,23 +4124,23 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <f aca="false">IF(Notes!$B$4="Yes",Notes!$B$5+Notes!$B$6+Notes!$B$7,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>148</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="16" t="n">
-        <f aca="false">Notes!$B$8</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4116,23 +4148,23 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E32" s="16" t="n">
         <f aca="false">Notes!$B$8</f>
         <v>0</v>
       </c>
+      <c r="F32" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G32" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4140,23 +4172,23 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <f aca="false">Notes!$B$9</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <f aca="false">Notes!$B$8</f>
         <v>0</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4164,44 +4196,68 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="E34" s="16" t="n">
         <f aca="false">Notes!$B$9</f>
         <v>0</v>
       </c>
+      <c r="F34" s="6" t="n">
+        <v>0</v>
+      </c>
       <c r="G34" s="5" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <f aca="false">SUM(E2:E34)</f>
-        <v>548862.99</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <f aca="false">SUM(F2:F34)</f>
-        <v>548862.99</v>
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <f aca="false">Notes!$B$9</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="2" t="s">
-        <v>152</v>
+        <v>110</v>
       </c>
       <c r="E36" s="14" t="n">
-        <f aca="false">ROUND(E35-F35,2)</f>
+        <f aca="false">SUM(E2:E35)</f>
+        <v>548862.99</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <f aca="false">SUM(F2:F35)</f>
+        <v>548862.99</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D37" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <f aca="false">ROUND(E36-F36,2)</f>
         <v>0</v>
       </c>
     </row>
@@ -4236,55 +4292,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="I4" s="20" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="J4" s="20" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K4" s="20" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B5" s="22" t="n">
         <v>0</v>
@@ -4323,12 +4379,12 @@
         <v>Reconciled</v>
       </c>
       <c r="L5" s="21" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B6" s="23" t="n">
         <f aca="false">F5</f>
@@ -4368,12 +4424,12 @@
         <v>Reconciled</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B7" s="23" t="n">
         <f aca="false">F6</f>
@@ -4413,12 +4469,12 @@
         <v>Reconciled</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B8" s="23" t="n">
         <f aca="false">F7</f>
@@ -4446,19 +4502,19 @@
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="23" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K8" s="21" t="str">
         <f aca="false">IF(AND(G8=0,OR(J8=0,J8="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
       <c r="L8" s="21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B9" s="23" t="n">
         <f aca="false">F8</f>
@@ -4486,19 +4542,19 @@
       <c r="H9" s="22"/>
       <c r="I9" s="22"/>
       <c r="J9" s="23" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K9" s="21" t="str">
         <f aca="false">IF(AND(G9=0,OR(J9=0,J9="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
       <c r="L9" s="21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B10" s="23" t="n">
         <f aca="false">F9</f>
@@ -4526,19 +4582,19 @@
       <c r="H10" s="22"/>
       <c r="I10" s="22"/>
       <c r="J10" s="23" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="K10" s="21" t="str">
         <f aca="false">IF(AND(G10=0,OR(J10=0,J10="n/a")),"Reconciled","CHECK")</f>
         <v>Reconciled</v>
       </c>
       <c r="L10" s="21" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="25" t="n">
@@ -4569,7 +4625,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D13" s="26" t="n">
         <f aca="false">COUNTIF('Monzo Transactions'!M2:M37,"&lt;&gt;0")</f>
@@ -4611,46 +4667,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4662,19 +4718,19 @@
         <v>2025-09</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D2" s="28" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E2" s="28" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F2" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G2" s="28" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H2" s="29" t="n">
         <f aca="false">IF(J2&gt;0,J2,0)</f>
@@ -4699,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="N2" s="28" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4711,19 +4767,19 @@
         <v>2025-09</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G3" s="28" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H3" s="29" t="n">
         <f aca="false">IF(J3&gt;0,J3,0)</f>
@@ -4748,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="N3" s="28" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4760,19 +4816,19 @@
         <v>2025-09</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D4" s="28" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E4" s="28" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F4" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H4" s="29" t="n">
         <f aca="false">IF(J4&gt;0,J4,0)</f>
@@ -4797,7 +4853,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="28" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4809,19 +4865,19 @@
         <v>2025-09</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H5" s="29" t="n">
         <f aca="false">IF(J5&gt;0,J5,0)</f>
@@ -4846,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="N5" s="28" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4858,19 +4914,19 @@
         <v>2025-10</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D6" s="28" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="H6" s="29" t="n">
         <f aca="false">IF(J6&gt;0,J6,0)</f>
@@ -4895,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4907,19 +4963,19 @@
         <v>2025-10</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F7" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H7" s="29" t="n">
         <f aca="false">IF(J7&gt;0,J7,0)</f>
@@ -4944,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4956,19 +5012,19 @@
         <v>2025-10</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D8" s="28" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E8" s="28" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="G8" s="28" t="s">
         <v>203</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="28" t="s">
-        <v>196</v>
       </c>
       <c r="H8" s="29" t="n">
         <f aca="false">IF(J8&gt;0,J8,0)</f>
@@ -4993,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5005,19 +5061,19 @@
         <v>2025-10</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H9" s="29" t="n">
         <f aca="false">IF(J9&gt;0,J9,0)</f>
@@ -5042,7 +5098,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5054,19 +5110,19 @@
         <v>2025-10</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H10" s="29" t="n">
         <f aca="false">IF(J10&gt;0,J10,0)</f>
@@ -5091,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5103,19 +5159,19 @@
         <v>2025-10</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H11" s="29" t="n">
         <f aca="false">IF(J11&gt;0,J11,0)</f>
@@ -5140,7 +5196,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5152,19 +5208,19 @@
         <v>2025-10</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H12" s="29" t="n">
         <f aca="false">IF(J12&gt;0,J12,0)</f>
@@ -5189,7 +5245,7 @@
         <v>0</v>
       </c>
       <c r="N12" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5201,19 +5257,19 @@
         <v>2025-10</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F13" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H13" s="29" t="n">
         <f aca="false">IF(J13&gt;0,J13,0)</f>
@@ -5238,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="N13" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5250,19 +5306,19 @@
         <v>2025-10</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H14" s="29" t="n">
         <f aca="false">IF(J14&gt;0,J14,0)</f>
@@ -5287,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5299,19 +5355,19 @@
         <v>2025-11</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H15" s="29" t="n">
         <f aca="false">IF(J15&gt;0,J15,0)</f>
@@ -5336,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5348,19 +5404,19 @@
         <v>2025-11</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D16" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F16" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H16" s="29" t="n">
         <f aca="false">IF(J16&gt;0,J16,0)</f>
@@ -5385,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5397,19 +5453,19 @@
         <v>2025-11</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F17" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H17" s="29" t="n">
         <f aca="false">IF(J17&gt;0,J17,0)</f>
@@ -5434,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="28" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5446,19 +5502,19 @@
         <v>2025-12</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D18" s="28" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H18" s="29" t="n">
         <f aca="false">IF(J18&gt;0,J18,0)</f>
@@ -5483,7 +5539,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5495,19 +5551,19 @@
         <v>2025-12</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H19" s="29" t="n">
         <f aca="false">IF(J19&gt;0,J19,0)</f>
@@ -5532,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="N19" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5544,19 +5600,19 @@
         <v>2025-12</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G20" s="28" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H20" s="29" t="n">
         <f aca="false">IF(J20&gt;0,J20,0)</f>
@@ -5581,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="N20" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5593,19 +5649,19 @@
         <v>2025-12</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H21" s="29" t="n">
         <f aca="false">IF(J21&gt;0,J21,0)</f>
@@ -5630,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5642,19 +5698,19 @@
         <v>2025-12</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H22" s="29" t="n">
         <f aca="false">IF(J22&gt;0,J22,0)</f>
@@ -5679,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5691,19 +5747,19 @@
         <v>2025-12</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H23" s="29" t="n">
         <f aca="false">IF(J23&gt;0,J23,0)</f>
@@ -5728,7 +5784,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5740,19 +5796,19 @@
         <v>2025-12</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D24" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E24" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F24" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H24" s="29" t="n">
         <f aca="false">IF(J24&gt;0,J24,0)</f>
@@ -5777,7 +5833,7 @@
         <v>0</v>
       </c>
       <c r="N24" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5789,19 +5845,19 @@
         <v>2025-12</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F25" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H25" s="29" t="n">
         <f aca="false">IF(J25&gt;0,J25,0)</f>
@@ -5826,7 +5882,7 @@
         <v>0</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5838,19 +5894,19 @@
         <v>2025-12</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F26" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H26" s="29" t="n">
         <f aca="false">IF(J26&gt;0,J26,0)</f>
@@ -5875,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="N26" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5887,19 +5943,19 @@
         <v>2026-01</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F27" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H27" s="29" t="n">
         <f aca="false">IF(J27&gt;0,J27,0)</f>
@@ -5924,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5936,19 +5992,19 @@
         <v>2026-01</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F28" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G28" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H28" s="29" t="n">
         <f aca="false">IF(J28&gt;0,J28,0)</f>
@@ -5973,7 +6029,7 @@
         <v>0</v>
       </c>
       <c r="N28" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5985,19 +6041,19 @@
         <v>2026-01</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H29" s="29" t="n">
         <f aca="false">IF(J29&gt;0,J29,0)</f>
@@ -6022,7 +6078,7 @@
         <v>0</v>
       </c>
       <c r="N29" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6034,19 +6090,19 @@
         <v>2026-01</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="H30" s="29" t="n">
         <f aca="false">IF(J30&gt;0,J30,0)</f>
@@ -6071,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="N30" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6083,19 +6139,19 @@
         <v>2026-01</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H31" s="29" t="n">
         <f aca="false">IF(J31&gt;0,J31,0)</f>
@@ -6120,7 +6176,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6132,19 +6188,19 @@
         <v>2026-01</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G32" s="28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H32" s="29" t="n">
         <f aca="false">IF(J32&gt;0,J32,0)</f>
@@ -6169,7 +6225,7 @@
         <v>0</v>
       </c>
       <c r="N32" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6181,19 +6237,19 @@
         <v>2026-01</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D33" s="28" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G33" s="28" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H33" s="29" t="n">
         <f aca="false">IF(J33&gt;0,J33,0)</f>
@@ -6218,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="N33" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6230,19 +6286,19 @@
         <v>2026-02</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="D34" s="28" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G34" s="28" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H34" s="29" t="n">
         <f aca="false">IF(J34&gt;0,J34,0)</f>
@@ -6267,7 +6323,7 @@
         <v>0</v>
       </c>
       <c r="N34" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6279,19 +6335,19 @@
         <v>2026-02</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D35" s="28" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="E35" s="28" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F35" s="28" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G35" s="28" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="H35" s="29" t="n">
         <f aca="false">IF(J35&gt;0,J35,0)</f>
@@ -6316,7 +6372,7 @@
         <v>0</v>
       </c>
       <c r="N35" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6328,19 +6384,19 @@
         <v>2026-02</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D36" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E36" s="28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="F36" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G36" s="28" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H36" s="29" t="n">
         <f aca="false">IF(J36&gt;0,J36,0)</f>
@@ -6365,7 +6421,7 @@
         <v>0</v>
       </c>
       <c r="N36" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6377,19 +6433,19 @@
         <v>2026-02</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D37" s="28" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E37" s="28" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F37" s="28" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="G37" s="28" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="H37" s="29" t="n">
         <f aca="false">IF(J37&gt;0,J37,0)</f>
@@ -6414,12 +6470,12 @@
         <v>0</v>
       </c>
       <c r="N37" s="28" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G38" s="26" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H38" s="31" t="n">
         <f aca="false">SUM(H2:H37)</f>
@@ -6464,49 +6520,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="19" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="B4" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="G4" s="32" t="s">
-        <v>177</v>
-      </c>
       <c r="H4" s="32" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="I4" s="32" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B5" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A5,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6544,7 +6600,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="B6" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A6,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6579,12 +6635,12 @@
         <v>4</v>
       </c>
       <c r="J6" s="35" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B7" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A7,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6619,12 +6675,12 @@
         <v>3</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B8" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A8,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6659,12 +6715,12 @@
         <v>6</v>
       </c>
       <c r="J8" s="35" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B9" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A9,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6699,12 +6755,12 @@
         <v>3</v>
       </c>
       <c r="J9" s="35" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B10" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A10,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6742,7 +6798,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B11" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A11,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6780,7 +6836,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="B12" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A12,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6818,7 +6874,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B13" s="33" t="n">
         <f aca="false">SUMIFS('Monzo Transactions'!$J:$J,'Monzo Transactions'!$G:$G,$A13,'Monzo Transactions'!$B:$B,B$4)</f>
@@ -6853,12 +6909,12 @@
         <v>2</v>
       </c>
       <c r="J13" s="35" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B14" s="25" t="n">
         <f aca="false">SUM(B5:B13)</f>
@@ -6896,7 +6952,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B15" s="37" t="n">
         <f aca="false">ROUND(B14-('Monzo Reconciliation'!C5-'Monzo Reconciliation'!D5),2)</f>
@@ -6942,1072 +6998,1072 @@
   <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="17" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="17" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="17" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="17" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C2" s="38" t="n">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="30" t="n">
         <v>133528</v>
       </c>
-      <c r="D2" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="39" t="n">
+      <c r="D2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="29" t="n">
         <f aca="false">D2+E2</f>
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C3" s="38" t="n">
+      <c r="G2" s="28" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="D3" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="39" t="n">
+      <c r="D3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="29" t="n">
         <f aca="false">D3+E3</f>
         <v>0</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C4" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="38" t="n">
+      <c r="G3" s="28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30" t="n">
         <v>650</v>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="30" t="n">
         <v>130</v>
       </c>
-      <c r="F4" s="39" t="n">
+      <c r="F4" s="29" t="n">
         <f aca="false">D4+E4</f>
         <v>780</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="G4" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="C5" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="38" t="n">
+      <c r="B5" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="29" t="n">
         <f aca="false">D5+E5</f>
         <v>42</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C6" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="38" t="n">
+      <c r="G5" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="29" t="n">
         <f aca="false">D6+E6</f>
         <v>240</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="C7" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="38" t="n">
+      <c r="G6" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>273</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="29" t="n">
         <f aca="false">D7+E7</f>
         <v>360</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="38" t="n">
+      <c r="G7" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="30" t="n">
         <v>29</v>
       </c>
-      <c r="E8" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="39" t="n">
+      <c r="E8" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29" t="n">
         <f aca="false">D8+E8</f>
         <v>29</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="38" t="n">
+      <c r="G8" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="E9" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="39" t="n">
+      <c r="E9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="29" t="n">
         <f aca="false">D9+E9</f>
         <v>18</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="38" t="n">
+      <c r="G9" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="E10" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="39" t="n">
+      <c r="E10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="29" t="n">
         <f aca="false">D10+E10</f>
         <v>45</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="G10" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="C11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="38" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="E11" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="39" t="n">
+      <c r="E11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="29" t="n">
         <f aca="false">D11+E11</f>
         <v>14</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="38" t="n">
+      <c r="G11" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="39" t="n">
+      <c r="E12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="29" t="n">
         <f aca="false">D12+E12</f>
         <v>7</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C13" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="38" t="n">
+      <c r="G12" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="E13" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="39" t="n">
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="29" t="n">
         <f aca="false">D13+E13</f>
         <v>45</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="38" t="n">
+      <c r="G13" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="E14" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="39" t="n">
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="29" t="n">
         <f aca="false">D14+E14</f>
         <v>15</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="C15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="38" t="n">
+      <c r="G14" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="E15" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="39" t="n">
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="29" t="n">
         <f aca="false">D15+E15</f>
         <v>15</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="38" t="n">
+      <c r="G15" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="E16" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="39" t="n">
+      <c r="E16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="29" t="n">
         <f aca="false">D16+E16</f>
         <v>60</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C17" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="38" t="n">
+      <c r="G16" s="28" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B17" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
         <v>131958</v>
       </c>
-      <c r="E17" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="39" t="n">
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="29" t="n">
         <f aca="false">D17+E17</f>
         <v>131958</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="38" t="n">
+      <c r="G17" s="28" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>286</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
         <v>462000</v>
       </c>
-      <c r="E18" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="n">
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="29" t="n">
         <f aca="false">D18+E18</f>
         <v>462000</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C19" s="38" t="n">
+      <c r="G18" s="28" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B19" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" s="30" t="n">
         <v>400</v>
       </c>
-      <c r="D19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="39" t="n">
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="29" t="n">
         <f aca="false">D19+E19</f>
         <v>0</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="38" t="n">
+      <c r="G19" s="28" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="30" t="n">
         <v>311938.6</v>
       </c>
-      <c r="D20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="39" t="n">
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="29" t="n">
         <f aca="false">D20+E20</f>
         <v>0</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="G20" s="28" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="28" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>131958</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="29" t="n">
+        <f aca="false">D21+E21</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="C21" s="38" t="n">
-        <v>131958</v>
-      </c>
-      <c r="D21" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="39" t="n">
-        <f aca="false">D21+E21</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B22" s="5" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="B22" s="28" t="s">
+        <v>292</v>
+      </c>
+      <c r="C22" s="30" t="n">
         <v>18362.34</v>
       </c>
-      <c r="D22" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="39" t="n">
+      <c r="D22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="29" t="n">
         <f aca="false">D22+E22</f>
         <v>0</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="C23" s="38" t="n">
+      <c r="G22" s="28" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" s="28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C23" s="30" t="n">
         <v>38000</v>
       </c>
-      <c r="D23" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="39" t="n">
+      <c r="D23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="29" t="n">
         <f aca="false">D23+E23</f>
         <v>0</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C24" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="38" t="n">
+      <c r="G23" s="28" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="30" t="n">
         <v>775</v>
       </c>
-      <c r="E24" s="38" t="n">
+      <c r="E24" s="30" t="n">
         <v>155</v>
       </c>
-      <c r="F24" s="39" t="n">
+      <c r="F24" s="29" t="n">
         <f aca="false">D24+E24</f>
         <v>930</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C25" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="38" t="n">
+      <c r="G24" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="E25" s="38" t="n">
+      <c r="E25" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="F25" s="39" t="n">
+      <c r="F25" s="29" t="n">
         <f aca="false">D25+E25</f>
         <v>120</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C26" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="38" t="n">
+      <c r="G25" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="30" t="n">
         <v>35</v>
       </c>
-      <c r="E26" s="38" t="n">
+      <c r="E26" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="39" t="n">
+      <c r="F26" s="29" t="n">
         <f aca="false">D26+E26</f>
         <v>42</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C27" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="38" t="n">
+      <c r="G26" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="E27" s="38" t="n">
+      <c r="E27" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="F27" s="39" t="n">
+      <c r="F27" s="29" t="n">
         <f aca="false">D27+E27</f>
         <v>90</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C28" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="38" t="n">
+      <c r="G27" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="E28" s="38" t="n">
+      <c r="E28" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="F28" s="39" t="n">
+      <c r="F28" s="29" t="n">
         <f aca="false">D28+E28</f>
         <v>72</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="38" t="n">
+      <c r="G28" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="E29" s="38" t="n">
+      <c r="E29" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="F29" s="39" t="n">
+      <c r="F29" s="29" t="n">
         <f aca="false">D29+E29</f>
         <v>360</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C30" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="38" t="n">
+      <c r="G29" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="38" t="n">
+      <c r="E30" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F30" s="39" t="n">
+      <c r="F30" s="29" t="n">
         <f aca="false">D30+E30</f>
         <v>60</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="38" t="n">
+      <c r="G30" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="E31" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="39" t="n">
+      <c r="E31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="29" t="n">
         <f aca="false">D31+E31</f>
         <v>7</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C32" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="38" t="n">
+      <c r="G31" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="E32" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="39" t="n">
+      <c r="E32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="29" t="n">
         <f aca="false">D32+E32</f>
         <v>18</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="C33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="38" t="n">
+      <c r="G32" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="E33" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="39" t="n">
+      <c r="E33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="29" t="n">
         <f aca="false">D33+E33</f>
         <v>45</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C34" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="38" t="n">
+      <c r="G33" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>305</v>
+      </c>
+      <c r="C34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="30" t="n">
         <v>109.66</v>
       </c>
-      <c r="E34" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="39" t="n">
+      <c r="E34" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="29" t="n">
         <f aca="false">D34+E34</f>
         <v>109.66</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C35" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="38" t="n">
+      <c r="G34" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="30" t="n">
         <v>150</v>
       </c>
-      <c r="E35" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="39" t="n">
+      <c r="E35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="29" t="n">
         <f aca="false">D35+E35</f>
         <v>150</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="C36" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="38" t="n">
+      <c r="G35" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="30" t="n">
         <v>36200</v>
       </c>
-      <c r="E36" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="39" t="n">
+      <c r="E36" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="29" t="n">
         <f aca="false">D36+E36</f>
         <v>36200</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C37" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="38" t="n">
+      <c r="G36" s="28" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>308</v>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="30" t="n">
         <v>200.28</v>
       </c>
-      <c r="E37" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="39" t="n">
+      <c r="E37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="29" t="n">
         <f aca="false">D37+E37</f>
         <v>200.28</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="C38" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="38" t="n">
+      <c r="G37" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B38" s="28" t="s">
+        <v>309</v>
+      </c>
+      <c r="C38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="E38" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="39" t="n">
+      <c r="E38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="29" t="n">
         <f aca="false">D38+E38</f>
         <v>60</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C39" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="38" t="n">
+      <c r="G38" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="C39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="E39" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="39" t="n">
+      <c r="E39" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="29" t="n">
         <f aca="false">D39+E39</f>
         <v>15</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="C40" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="38" t="n">
+      <c r="G39" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>311</v>
+      </c>
+      <c r="C40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="E40" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="39" t="n">
+      <c r="E40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="29" t="n">
         <f aca="false">D40+E40</f>
         <v>20</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C41" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="38" t="n">
+      <c r="G40" s="28" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="30" t="n">
         <v>160</v>
       </c>
-      <c r="E41" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="39" t="n">
+      <c r="E41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="29" t="n">
         <f aca="false">D41+E41</f>
         <v>160</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
+      <c r="G41" s="28" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C45" s="39" t="n">
+      <c r="B44" s="38"/>
+      <c r="C44" s="32" t="s">
+        <v>314</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="G44" s="32" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="29" t="n">
         <f aca="false">SUMIFS($C$2:$C$41,$A$2:$A$41,$A45)</f>
         <v>133628</v>
       </c>
-      <c r="D45" s="38" t="n">
+      <c r="D45" s="30" t="n">
         <v>133628</v>
       </c>
-      <c r="E45" s="39" t="n">
+      <c r="E45" s="29" t="n">
         <f aca="false">SUMIFS($F$2:$F$41,$A$2:$A$41,$A45)</f>
         <v>133628</v>
       </c>
-      <c r="F45" s="38" t="n">
+      <c r="F45" s="30" t="n">
         <v>133628</v>
       </c>
-      <c r="G45" s="2" t="str">
+      <c r="G45" s="26" t="str">
         <f aca="false">IF(AND(ROUND(C45-D45,2)=0,ROUND(E45-F45,2)=0,ROUND(C45-E45,2)=0),"Agrees – balances to £0","CHECK")</f>
         <v>Agrees – balances to £0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C46" s="39" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="C46" s="29" t="n">
         <f aca="false">SUMIFS($C$2:$C$41,$A$2:$A$41,$A46)</f>
         <v>500658.94</v>
       </c>
-      <c r="D46" s="38" t="n">
+      <c r="D46" s="30" t="n">
         <v>500658.94</v>
       </c>
-      <c r="E46" s="39" t="n">
+      <c r="E46" s="29" t="n">
         <f aca="false">SUMIFS($F$2:$F$41,$A$2:$A$41,$A46)</f>
         <v>500658.94</v>
       </c>
-      <c r="F46" s="38" t="n">
+      <c r="F46" s="30" t="n">
         <v>500658.94</v>
       </c>
-      <c r="G46" s="2" t="str">
+      <c r="G46" s="26" t="str">
         <f aca="false">IF(AND(ROUND(C46-D46,2)=0,ROUND(E46-F46,2)=0,ROUND(C46-E46,2)=0),"Agrees – balances to £0","CHECK")</f>
         <v>Agrees – balances to £0</v>
       </c>
